--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.04839</v>
+        <v>17.40521</v>
       </c>
       <c r="D2" t="n">
-        <v>17.15179</v>
+        <v>16.71182</v>
       </c>
       <c r="E2" t="n">
-        <v>17.12121</v>
+        <v>16.95027</v>
       </c>
       <c r="F2" t="n">
-        <v>43.96063</v>
+        <v>43.91199</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05165</v>
+        <v>0.05236</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84295</v>
+        <v>1.86985</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.28856</v>
+        <v>17.47667</v>
       </c>
       <c r="D3" t="n">
-        <v>17.51614</v>
+        <v>16.99932</v>
       </c>
       <c r="E3" t="n">
-        <v>17.21415</v>
+        <v>17.15721</v>
       </c>
       <c r="F3" t="n">
-        <v>43.60089</v>
+        <v>43.8222</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05229</v>
+        <v>0.05184</v>
       </c>
       <c r="H3" t="n">
-        <v>1.89769</v>
+        <v>1.86749</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.48503</v>
+        <v>17.22792</v>
       </c>
       <c r="D4" t="n">
-        <v>17.31421</v>
+        <v>16.96983</v>
       </c>
       <c r="E4" t="n">
-        <v>17.28677</v>
+        <v>17.03184</v>
       </c>
       <c r="F4" t="n">
-        <v>43.22621</v>
+        <v>44.36653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05248</v>
+        <v>0.05178</v>
       </c>
       <c r="H4" t="n">
-        <v>1.89013</v>
+        <v>1.90102</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.06817</v>
+        <v>17.15676</v>
       </c>
       <c r="D6" t="n">
-        <v>16.56228</v>
+        <v>16.61329</v>
       </c>
       <c r="E6" t="n">
-        <v>16.5431</v>
+        <v>16.67976</v>
       </c>
       <c r="F6" t="n">
-        <v>22.6576</v>
+        <v>22.28357</v>
       </c>
       <c r="G6" t="n">
-        <v>34.40216</v>
+        <v>35.39464</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.30989</v>
+        <v>16.8618</v>
       </c>
       <c r="D7" t="n">
-        <v>16.31005</v>
+        <v>16.51262</v>
       </c>
       <c r="E7" t="n">
-        <v>16.62794</v>
+        <v>16.78492</v>
       </c>
       <c r="F7" t="n">
-        <v>22.23368</v>
+        <v>22.84962</v>
       </c>
       <c r="G7" t="n">
-        <v>34.29879</v>
+        <v>35.62497</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.39261</v>
+        <v>17.07923</v>
       </c>
       <c r="D8" t="n">
-        <v>16.10395</v>
+        <v>16.51854</v>
       </c>
       <c r="E8" t="n">
-        <v>17.15153</v>
+        <v>16.82438</v>
       </c>
       <c r="F8" t="n">
-        <v>22.31818</v>
+        <v>22.18136</v>
       </c>
       <c r="G8" t="n">
-        <v>35.4245</v>
+        <v>35.332</v>
       </c>
     </row>
   </sheetData>
